--- a/data/2026/sectors_2026.xlsx
+++ b/data/2026/sectors_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naughtm\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2578FFC-1C1C-4C3E-A5D7-FEC3B5789845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD4853F-0E3E-4CFE-B6F7-A53846F8D69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="795" windowWidth="21600" windowHeight="11295" xr2:uid="{1525BEDA-ABA9-4F39-9C4C-2247DC58A9E5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1525BEDA-ABA9-4F39-9C4C-2247DC58A9E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>January</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>No Sector Entered</t>
+  </si>
+  <si>
+    <t>Economic Sector</t>
   </si>
 </sst>
 </file>
@@ -139,10 +142,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +176,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFED0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -211,9 +221,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -225,7 +235,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -569,6 +582,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1124,6 +1140,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="eDocument" ma:contentTypeID="0x0101000BC94875665D404BB1351B53C41FD2C000E5CBA74D75A77049B177D97877D56E03" ma:contentTypeVersion="199" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="f29b0ff1a26a7575c948acee1be83c00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f94102a1-1d6c-4502-ac27-91905b9321dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3fe347a261331acec84421138fd81903" ns2:_="">
     <xsd:import namespace="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
@@ -1332,15 +1357,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1381,6 +1397,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFBD2B2A-8D5D-4EB2-9D5C-D58B2A389226}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{299DDBF6-F686-44BE-BDDE-71B68F79A58D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1394,14 +1418,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFBD2B2A-8D5D-4EB2-9D5C-D58B2A389226}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
